--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2C座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22881,4748 +22743,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Deep Water South 第6A期 - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>184 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>17 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>153 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2011呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 335呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,116万
-$33,110/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,113万
-$33,033/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$955万
-$28,350/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$942万
-$27,964/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$940万
-$27,902/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$936万
-$27,786/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$934万
-$27,727/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,097万
-$32,552/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,095万
-$32,481/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,092万
-$32,415/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,090万
-$32,347/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,088万
-$32,279/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,086万
-$32,211/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,083万
-$32,142/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,079万
-$32,018/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,077万
-$31,953/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$957万
-$28,386/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,072万
-$31,825/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$910万
-$27,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$919万
-$27,261/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$917万
-$27,208/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$1,064万
-$31,570/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$913万
-$27,098/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$910万
-$26,991/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$897万
-$26,623/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$894万
-$26,516/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$892万
-$26,466/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$890万
-$26,412/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$888万
-$26,359/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 922呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 917呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 830呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 336呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="inlineStr">
-        <is>
-          <t>F | 337呎 (1房)
-$918万
-$27,234/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 874呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 870呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 784呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 299呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>E | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 300呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Deep Water South 第6A期 - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>124 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,221万
-$38,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$949万
-$28,163/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,243万
-$28,252/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,127万
-$33,144/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,213万
-$38,359/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$992万
-$29,421/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,240万
-$28,191/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$956万
-$28,115/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,206万
-$38,232/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$989万
-$29,359/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,296万
-$29,452/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$999万
-$29,371/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,935万
-$33,541/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$943万
-$27,982/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,235万
-$28,070/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$996万
-$29,309/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,863万
-$32,295/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$941万
-$27,920/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,232万
-$28,011/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$950万
-$27,935/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,178万
-$37,754/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$954万
-$28,294/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,227万
-$27,895/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$946万
-$27,818/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,846万
-$31,991/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$935万
-$27,745/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,225万
-$27,834/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$941万
-$27,676/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,840万
-$31,891/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$933万
-$27,688/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,222万
-$27,777/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$939万
-$27,618/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,834万
-$31,790/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$975万
-$28,932/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,277万
-$29,023/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$937万
-$27,559/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,829万
-$31,692/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$929万
-$27,573/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,260万
-$28,636/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$979万
-$28,794/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,844万
-$31,964/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$927万
-$27,513/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,272万
-$28,902/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,098万
-$32,285/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,138万
-$37,049/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$925万
-$27,457/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,212万
-$27,545/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,095万
-$32,218/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,131万
-$36,932/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$923万
-$27,398/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,209万
-$27,486/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,093万
-$32,150/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,869万
-$32,399/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$921万
-$27,341/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,250万
-$28,398/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,091万
-$32,082/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,795万
-$31,107/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$934万
-$27,715/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,202万
-$27,320/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,086万
-$31,956/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,105万
-$36,487/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$948万
-$28,136/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,200万
-$27,266/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$965万
-$28,385/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,784万
-$30,922/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$957万
-$28,401/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,197万
-$27,211/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,082万
-$31,829/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,779万
-$30,830/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$955万
-$28,344/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,195万
-$27,157/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,080万
-$31,765/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,774万
-$30,738/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$953万
-$28,288/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,192万
-$27,102/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,076万
-$31,638/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,831万
-$31,728/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$909万
-$26,961/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,190万
-$27,048/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,074万
-$31,576/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,763万
-$30,553/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$907万
-$26,908/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,244万
-$28,264/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$954万
-$28,047/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,758万
-$30,463/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$952万
-$28,255/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,247万
-$28,345/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,079万
-$31,735/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,752万
-$30,371/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$908万
-$26,932/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,189万
-$27,018/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,077万
-$31,671/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,742万
-$30,191/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$904万
-$26,822/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,226万
-$27,859/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,072万
-$31,544/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,767万
-$30,631/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$902万
-$26,772/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,182万
-$26,855/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,070万
-$31,482/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,732万
-$30,010/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$904万
-$26,822/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,218万
-$27,693/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,068万
-$31,418/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,721万
-$29,830/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$897万
-$26,611/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,230万
-$27,952/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,066万
-$31,356/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,019万
-$34,990/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$895万
-$26,555/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,172万
-$26,643/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,064万
-$31,294/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$2,013万
-$34,884/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$893万
-$26,501/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,225万
-$27,841/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$1,062万
-$31,229/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1,706万
-$29,563/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$933万
-$27,694/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>C | 440呎 (2房)
-$1,168万
-$26,536/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$901万
-$26,494/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 539呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 301呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>C | 401呎 (2房)
-$1,250万
-$31,172/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 302呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Deep Water South 第6A期 - 2C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>155 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>37 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>53 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>65 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,186万
-$38,831/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,145万
-$33,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,145万
-$28,702/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,179万
-$38,705/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$989万
-$28,906/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,183万
-$29,647/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,152万
-$38,233/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,140万
-$33,342/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,140万
-$28,576/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,146万
-$38,112/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,138万
-$33,272/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,138万
-$28,516/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,158万
-$38,336/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$965万
-$28,225/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,135万
-$28,456/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,145万
-$38,096/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,131万
-$33,064/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,170万
-$29,336/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,833万
-$32,556/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,125万
-$32,895/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,125万
-$28,193/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,796万
-$31,892/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$960万
-$28,070/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,123万
-$28,135/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,125万
-$37,737/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,120万
-$32,757/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,120万
-$28,075/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,811万
-$32,165/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,118万
-$32,690/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,157万
-$29,003/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,111万
-$37,501/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,116万
-$32,620/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,116万
-$27,957/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,789万
-$31,778/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,113万
-$32,553/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,152万
-$28,882/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,768万
-$31,394/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,111万
-$32,485/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,111万
-$27,840/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,845万
-$32,767/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,109万
-$32,415/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,161万
-$29,088/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,767万
-$31,389/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,104万
-$32,287/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,156万
-$28,972/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,073万
-$36,817/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,102万
-$32,219/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,154万
-$28,917/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$2,066万
-$36,705/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,100万
-$32,158/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,100万
-$27,561/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,736万
-$30,829/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,098万
-$32,096/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,098万
-$27,506/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,731万
-$30,739/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,093万
-$31,962/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,093万
-$27,396/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,725万
-$30,647/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,091万
-$31,904/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,091万
-$27,341/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,736万
-$30,829/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,089万
-$31,839/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,089万
-$27,286/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,731万
-$30,739/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,087万
-$31,778/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,087万
-$27,233/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,790万
-$31,801/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,084万
-$31,711/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,084万
-$27,178/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,700万
-$30,190/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,080万
-$31,585/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,080万
-$27,070/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,695万
-$30,099/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,078万
-$31,523/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,129万
-$28,288/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,705万
-$30,282/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,076万
-$31,462/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,076万
-$26,962/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,680万
-$29,831/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-$1,074万
-$31,395/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,074万
-$26,907/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,674万
-$29,742/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,078万
-$27,013/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,669万
-$29,652/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,107万
-$27,747/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 867呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 561呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>C | 563呎 (2房)
-$1,679万
-$29,829/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 342呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>E | 399呎 (2房)
-$1,067万
-$26,747/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 836呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 523呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 525呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 363呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2C座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +225,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -22743,4 +22924,4748 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2011呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 335呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1116万
+$33,110/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1113万
+$33,033/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$955万
+$28,350/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$942万
+$27,964/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$940万
+$27,902/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$936万
+$27,786/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$934万
+$27,727/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1097万
+$32,552/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1095万
+$32,481/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1092万
+$32,415/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1090万
+$32,347/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1088万
+$32,279/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1086万
+$32,211/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1083万
+$32,142/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1079万
+$32,018/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1077万
+$31,953/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$957万
+$28,386/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1072万
+$31,825/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$910万
+$27,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$919万
+$27,261/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$917万
+$27,208/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$1064万
+$31,570/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$913万
+$27,098/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$910万
+$26,991/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$897万
+$26,623/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$894万
+$26,516/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$892万
+$26,466/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$890万
+$26,412/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$888万
+$26,359/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 922呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 917呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 830呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 336呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$918万
+$27,234/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 874呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 870呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 784呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 300呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2221万
+$38,485/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$949万
+$28,163/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1243万
+$28,252/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1127万
+$33,144/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2213万
+$38,359/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$992万
+$29,421/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1240万
+$28,191/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$956万
+$28,115/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2206万
+$38,232/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$989万
+$29,359/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1296万
+$29,452/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$999万
+$29,371/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1935万
+$33,541/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$943万
+$27,982/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1235万
+$28,070/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$996万
+$29,309/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1863万
+$32,295/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$941万
+$27,920/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1232万
+$28,011/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$950万
+$27,935/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2178万
+$37,754/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$954万
+$28,294/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1227万
+$27,895/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$946万
+$27,818/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1846万
+$31,991/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$935万
+$27,745/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1225万
+$27,834/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$941万
+$27,676/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1840万
+$31,891/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$933万
+$27,688/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1222万
+$27,777/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$939万
+$27,618/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1834万
+$31,790/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$975万
+$28,932/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1277万
+$29,023/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$937万
+$27,559/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1829万
+$31,692/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$929万
+$27,573/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1260万
+$28,636/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$979万
+$28,794/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1844万
+$31,964/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$927万
+$27,513/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1272万
+$28,902/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1098万
+$32,285/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2138万
+$37,049/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$925万
+$27,457/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1212万
+$27,545/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1095万
+$32,218/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2131万
+$36,932/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$923万
+$27,398/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1209万
+$27,486/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1093万
+$32,150/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1869万
+$32,399/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$921万
+$27,341/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1250万
+$28,398/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1091万
+$32,082/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1795万
+$31,107/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$934万
+$27,715/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1202万
+$27,320/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1086万
+$31,956/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2105万
+$36,487/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$948万
+$28,136/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1200万
+$27,266/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$965万
+$28,385/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1784万
+$30,922/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$957万
+$28,401/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1197万
+$27,211/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1082万
+$31,829/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1779万
+$30,830/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$955万
+$28,344/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1195万
+$27,157/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1080万
+$31,765/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1774万
+$30,738/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$953万
+$28,288/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1192万
+$27,102/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1076万
+$31,638/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1831万
+$31,728/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$909万
+$26,961/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1190万
+$27,048/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1074万
+$31,576/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1763万
+$30,553/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$907万
+$26,908/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1244万
+$28,264/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$954万
+$28,047/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1758万
+$30,463/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$952万
+$28,255/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1247万
+$28,345/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1079万
+$31,735/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1752万
+$30,371/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$908万
+$26,932/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1189万
+$27,018/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1077万
+$31,671/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1742万
+$30,191/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$904万
+$26,822/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1226万
+$27,859/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1072万
+$31,544/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1767万
+$30,631/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$902万
+$26,772/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1182万
+$26,855/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1070万
+$31,482/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1732万
+$30,010/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$904万
+$26,822/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1218万
+$27,693/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1068万
+$31,418/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1721万
+$29,830/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$897万
+$26,611/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1230万
+$27,952/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1066万
+$31,356/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2019万
+$34,990/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$895万
+$26,555/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1172万
+$26,643/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1064万
+$31,294/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$2013万
+$34,884/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$893万
+$26,501/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1225万
+$27,841/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$1062万
+$31,229/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1706万
+$29,563/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$933万
+$27,694/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>C | 440呎 (2房)
+$1168万
+$26,536/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$901万
+$26,494/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 539呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>C | 401呎 (2房)
+$1250万
+$31,172/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 302呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2186万
+$38,831/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1145万
+$33,485/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1145万
+$28,702/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2179万
+$38,705/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$989万
+$28,906/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1183万
+$29,647/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2152万
+$38,233/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1140万
+$33,342/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1140万
+$28,576/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2146万
+$38,112/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1138万
+$33,272/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1138万
+$28,516/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2158万
+$38,336/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$965万
+$28,225/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1135万
+$28,456/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2145万
+$38,096/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1131万
+$33,064/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1170万
+$29,336/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1833万
+$32,556/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1125万
+$32,895/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1125万
+$28,193/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1796万
+$31,892/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$960万
+$28,070/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1123万
+$28,135/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2125万
+$37,737/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1120万
+$32,757/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1120万
+$28,075/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1811万
+$32,165/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1118万
+$32,690/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1157万
+$29,003/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2111万
+$37,501/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1116万
+$32,620/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1116万
+$27,957/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1789万
+$31,778/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1113万
+$32,553/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1152万
+$28,882/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1768万
+$31,394/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1111万
+$32,485/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1111万
+$27,840/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1845万
+$32,767/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1109万
+$32,415/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1161万
+$29,088/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1767万
+$31,389/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1104万
+$32,287/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1156万
+$28,972/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2073万
+$36,817/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1102万
+$32,219/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1154万
+$28,917/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$2066万
+$36,705/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1100万
+$32,158/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1100万
+$27,561/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1736万
+$30,829/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1098万
+$32,096/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1098万
+$27,506/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1731万
+$30,739/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1093万
+$31,962/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1093万
+$27,396/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1725万
+$30,647/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1091万
+$31,904/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1091万
+$27,341/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1736万
+$30,829/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1089万
+$31,839/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1089万
+$27,286/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1731万
+$30,739/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1087万
+$31,778/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1087万
+$27,233/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1790万
+$31,801/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1084万
+$31,711/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1084万
+$27,178/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1700万
+$30,190/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1080万
+$31,585/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1080万
+$27,070/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1695万
+$30,099/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1078万
+$31,523/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1129万
+$28,288/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1705万
+$30,282/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1076万
+$31,462/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1076万
+$26,962/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1680万
+$29,831/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+$1074万
+$31,395/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1074万
+$26,907/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1674万
+$29,742/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1078万
+$27,013/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1669万
+$29,652/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1107万
+$27,747/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 867呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 561呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>C | 563呎 (2房)
+$1679万
+$29,829/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 342呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>E | 399呎 (2房)
+$1067万
+$26,747/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 836呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 523呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 525呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 363呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -785,14 +785,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>9484300</v>
+        <v>9595880</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>28143</v>
+        <v>28474</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1057,14 +1057,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>9462200</v>
+        <v>9573520</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>28078</v>
+        <v>28408</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -3529,14 +3529,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>9324500</v>
+        <v>9434200</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>27669</v>
+        <v>27995</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3941,14 +3941,14 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>9304100</v>
+        <v>9413560</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>27609</v>
+        <v>27933</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -4353,14 +4353,14 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>9285400</v>
+        <v>9394640</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>27553</v>
+        <v>27877</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>9265850</v>
+        <v>9374860</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>27495</v>
+        <v>27819</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>9246300</v>
+        <v>9355080</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>27437</v>
+        <v>27760</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5589,14 +5589,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>9226750</v>
+        <v>9335300</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>27379</v>
+        <v>27701</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -6001,14 +6001,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>9207200</v>
+        <v>9315520</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>27321</v>
+        <v>27642</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6413,14 +6413,14 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>9171500</v>
+        <v>9279400</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>27215</v>
+        <v>27535</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>9152800</v>
+        <v>9260480</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>27160</v>
+        <v>27479</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -7649,14 +7649,14 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>9116250</v>
+        <v>9223500</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>27051</v>
+        <v>27369</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -9297,14 +9297,14 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
-        <v>9043150</v>
+        <v>9149540</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>26834</v>
+        <v>27150</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -13425,14 +13425,14 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>9578650</v>
+        <v>9691340</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>28172</v>
+        <v>28504</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -13611,14 +13611,14 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>18875100</v>
+        <v>19097160</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>32712</v>
+        <v>33097</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -13859,14 +13859,14 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>18813050</v>
+        <v>19034380</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>32605</v>
+        <v>32989</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -14107,14 +14107,14 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>18751000</v>
+        <v>18971600</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>32497</v>
+        <v>32880</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -14851,14 +14851,14 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>18516400</v>
+        <v>18734240</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>32091</v>
+        <v>32468</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
@@ -15905,14 +15905,14 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>9330450</v>
+        <v>9440220</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>27442</v>
+        <v>27765</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -16153,14 +16153,14 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>9310900</v>
+        <v>9420440</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>27385</v>
+        <v>27707</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -16339,14 +16339,14 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
-        <v>18170450</v>
+        <v>18384220</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>31491</v>
+        <v>31862</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -16401,14 +16401,14 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>9291350</v>
+        <v>9400660</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>27328</v>
+        <v>27649</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -16587,14 +16587,14 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
-        <v>18113500</v>
+        <v>18326600</v>
       </c>
       <c r="L238" s="5" t="n">
-        <v>31393</v>
+        <v>31762</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -16649,14 +16649,14 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>9271800</v>
+        <v>9380880</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>27270</v>
+        <v>27591</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -16897,14 +16897,14 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>9235250</v>
+        <v>9343900</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>27162</v>
+        <v>27482</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -17331,14 +17331,14 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>17895050</v>
+        <v>18105580</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>31014</v>
+        <v>31379</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -17393,14 +17393,14 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>9198700</v>
+        <v>9306920</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>27055</v>
+        <v>27373</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -17641,14 +17641,14 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K255" s="5" t="n">
-        <v>9180000</v>
+        <v>9288000</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>27000</v>
+        <v>27318</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
@@ -17889,14 +17889,14 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>9143450</v>
+        <v>9251020</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>26892</v>
+        <v>27209</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -18137,14 +18137,14 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>9125600</v>
+        <v>9232960</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>26840</v>
+        <v>27156</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -20307,14 +20307,14 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K298" s="5" t="n">
-        <v>17160650</v>
+        <v>17362540</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>29741</v>
+        <v>30091</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
@@ -20555,14 +20555,14 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K302" s="5" t="n">
-        <v>17108800</v>
+        <v>17310080</v>
       </c>
       <c r="L302" s="5" t="n">
-        <v>29651</v>
+        <v>30000</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
@@ -21913,14 +21913,14 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
-        <v>18296250</v>
+        <v>18511500</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>32498</v>
+        <v>32880</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -22239,14 +22239,14 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K328" s="5" t="n">
-        <v>18238450</v>
+        <v>18453020</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>32395</v>
+        <v>32776</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -10110,7 +10110,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -32678,7 +32678,7 @@
           <t>F | 337呎 (1房)
 $910万
 $26,991/呎
-(26年-06月-24日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35072,7 @@
           <t>C | 563呎 (2房)
 $1789万
 $31,778/呎
-(26年-06月-20日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
@@ -17315,34 +17315,34 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
-        <v>21053000</v>
+        <v>18738000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>36487</v>
+        <v>32475</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>18105580</v>
+        <v>18738000</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>31379</v>
+        <v>32475</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K255" s="5" t="n">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
@@ -18560,14 +18560,14 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
-        <v>17629000</v>
+        <v>18459000</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>30553</v>
+        <v>31991</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
@@ -18575,10 +18575,10 @@
         </is>
       </c>
       <c r="K270" s="5" t="n">
-        <v>17629000</v>
+        <v>18459000</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>30553</v>
+        <v>31991</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K298" s="5" t="n">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K302" s="5" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="K328" s="5" t="n">
@@ -32513,7 +32513,7 @@
           <t>F | 337呎 (1房)
 $917万
 $27,208/呎
-(26年-06月-21日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -33139,7 +33139,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -33149,7 +33149,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -33781,12 +33781,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
-$2105万
-$36,487/呎
-(在售)</t>
+$1874万
+$32,475/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -33979,9 +33979,9 @@
       <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
-$1763万
-$30,553/呎
-(26年-05月-31日)</t>
+$1846万
+$31,991/呎
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -31523,7 +31523,7 @@
           <t>F | 337呎 (1房)
 $955万
 $28,350/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
           <t>F | 337呎 (1房)
 $942万
 $27,964/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -31633,7 +31633,7 @@
           <t>F | 337呎 (1房)
 $940万
 $27,902/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31688,7 @@
           <t>F | 337呎 (1房)
 $936万
 $27,786/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -31743,7 +31743,7 @@
           <t>F | 337呎 (1房)
 $934万
 $27,727/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32293,7 +32293,7 @@
           <t>F | 337呎 (1房)
 $957万
 $28,386/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -32403,7 +32403,7 @@
           <t>F | 337呎 (1房)
 $910万
 $27,000/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32458,7 +32458,7 @@
           <t>F | 337呎 (1房)
 $919万
 $27,261/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32513,7 @@
           <t>F | 337呎 (1房)
 $917万
 $27,208/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
           <t>F | 337呎 (1房)
 $913万
 $27,098/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32678,7 +32678,7 @@
           <t>F | 337呎 (1房)
 $910万
 $26,991/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -32733,7 +32733,7 @@
           <t>F | 337呎 (1房)
 $897万
 $26,623/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -32788,7 +32788,7 @@
           <t>F | 337呎 (1房)
 $894万
 $26,516/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32843,7 +32843,7 @@
           <t>F | 337呎 (1房)
 $892万
 $26,466/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
           <t>F | 337呎 (1房)
 $890万
 $26,412/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -32953,7 +32953,7 @@
           <t>F | 337呎 (1房)
 $888万
 $26,359/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -33008,7 +33008,7 @@
           <t>F | 337呎 (1房)
 $918万
 $27,234/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
           <t>B | 337呎 (1房)
 $949万
 $28,163/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -33217,7 +33217,7 @@
           <t>C | 440呎 (2房)
 $1243万
 $28,252/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -33248,7 +33248,7 @@
           <t>B | 337呎 (1房)
 $992万
 $29,421/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -33256,7 +33256,7 @@
           <t>C | 440呎 (2房)
 $1240万
 $28,191/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -33264,7 +33264,7 @@
           <t>D | 340呎 (1房)
 $956万
 $28,115/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -33287,7 +33287,7 @@
           <t>B | 337呎 (1房)
 $989万
 $29,359/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -33295,7 +33295,7 @@
           <t>C | 440呎 (2房)
 $1296万
 $29,452/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -33303,7 +33303,7 @@
           <t>D | 340呎 (1房)
 $999万
 $29,371/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -33318,7 +33318,7 @@
           <t>A | 577呎 (2房)
 $1935万
 $33,541/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -33326,7 +33326,7 @@
           <t>B | 337呎 (1房)
 $943万
 $27,982/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -33334,7 +33334,7 @@
           <t>C | 440呎 (2房)
 $1235万
 $28,070/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -33342,7 +33342,7 @@
           <t>D | 340呎 (1房)
 $996万
 $29,309/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
           <t>A | 577呎 (2房)
 $1863万
 $32,295/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -33365,7 +33365,7 @@
           <t>B | 337呎 (1房)
 $941万
 $27,920/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -33373,7 +33373,7 @@
           <t>C | 440呎 (2房)
 $1232万
 $28,011/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -33381,7 +33381,7 @@
           <t>D | 340呎 (1房)
 $950万
 $27,935/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -33404,7 +33404,7 @@
           <t>B | 337呎 (1房)
 $954万
 $28,294/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -33412,7 +33412,7 @@
           <t>C | 440呎 (2房)
 $1227万
 $27,895/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -33420,7 +33420,7 @@
           <t>D | 340呎 (1房)
 $946万
 $27,818/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -33435,7 +33435,7 @@
           <t>A | 577呎 (2房)
 $1846万
 $31,991/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -33443,7 +33443,7 @@
           <t>B | 337呎 (1房)
 $935万
 $27,745/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -33451,7 +33451,7 @@
           <t>C | 440呎 (2房)
 $1225万
 $27,834/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -33459,7 +33459,7 @@
           <t>D | 340呎 (1房)
 $941万
 $27,676/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -33474,7 +33474,7 @@
           <t>A | 577呎 (2房)
 $1840万
 $31,891/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -33482,7 +33482,7 @@
           <t>B | 337呎 (1房)
 $933万
 $27,688/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -33490,7 +33490,7 @@
           <t>C | 440呎 (2房)
 $1222万
 $27,777/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -33498,7 +33498,7 @@
           <t>D | 340呎 (1房)
 $939万
 $27,618/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -33513,7 +33513,7 @@
           <t>A | 577呎 (2房)
 $1834万
 $31,790/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -33521,7 +33521,7 @@
           <t>B | 337呎 (1房)
 $975万
 $28,932/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -33529,7 +33529,7 @@
           <t>C | 440呎 (2房)
 $1277万
 $29,023/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -33537,7 +33537,7 @@
           <t>D | 340呎 (1房)
 $937万
 $27,559/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -33552,7 +33552,7 @@
           <t>A | 577呎 (2房)
 $1829万
 $31,692/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -33560,7 +33560,7 @@
           <t>B | 337呎 (1房)
 $929万
 $27,573/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -33568,7 +33568,7 @@
           <t>C | 440呎 (2房)
 $1260万
 $28,636/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -33576,7 +33576,7 @@
           <t>D | 340呎 (1房)
 $979万
 $28,794/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
           <t>A | 577呎 (2房)
 $1844万
 $31,964/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -33599,7 +33599,7 @@
           <t>B | 337呎 (1房)
 $927万
 $27,513/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -33607,7 +33607,7 @@
           <t>C | 440呎 (2房)
 $1272万
 $28,902/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -33638,7 +33638,7 @@
           <t>B | 337呎 (1房)
 $925万
 $27,457/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -33646,7 +33646,7 @@
           <t>C | 440呎 (2房)
 $1212万
 $27,545/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>B | 337呎 (1房)
 $923万
 $27,398/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -33685,7 +33685,7 @@
           <t>C | 440呎 (2房)
 $1209万
 $27,486/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>A | 577呎 (2房)
 $1869万
 $32,399/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>B | 337呎 (1房)
 $921万
 $27,341/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -33724,7 +33724,7 @@
           <t>C | 440呎 (2房)
 $1250万
 $28,398/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -33747,7 +33747,7 @@
           <t>A | 577呎 (2房)
 $1795万
 $31,107/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -33755,7 +33755,7 @@
           <t>B | 337呎 (1房)
 $934万
 $27,715/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -33763,7 +33763,7 @@
           <t>C | 440呎 (2房)
 $1202万
 $27,320/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -33786,7 +33786,7 @@
           <t>A | 577呎 (2房)
 $1874万
 $32,475/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -33794,7 +33794,7 @@
           <t>B | 337呎 (1房)
 $948万
 $28,136/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -33802,7 +33802,7 @@
           <t>C | 440呎 (2房)
 $1200万
 $27,266/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -33810,7 +33810,7 @@
           <t>D | 340呎 (1房)
 $965万
 $28,385/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -33825,7 +33825,7 @@
           <t>A | 577呎 (2房)
 $1784万
 $30,922/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -33833,7 +33833,7 @@
           <t>B | 337呎 (1房)
 $957万
 $28,401/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -33841,7 +33841,7 @@
           <t>C | 440呎 (2房)
 $1197万
 $27,211/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -33864,7 +33864,7 @@
           <t>A | 577呎 (2房)
 $1779万
 $30,830/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -33872,7 +33872,7 @@
           <t>B | 337呎 (1房)
 $955万
 $28,344/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -33880,7 +33880,7 @@
           <t>C | 440呎 (2房)
 $1195万
 $27,157/呎
-(26年-03月-21日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -33903,7 +33903,7 @@
           <t>A | 577呎 (2房)
 $1774万
 $30,738/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -33911,7 +33911,7 @@
           <t>B | 337呎 (1房)
 $953万
 $28,288/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -33919,7 +33919,7 @@
           <t>C | 440呎 (2房)
 $1192万
 $27,102/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -33942,7 +33942,7 @@
           <t>A | 577呎 (2房)
 $1831万
 $31,728/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -33950,7 +33950,7 @@
           <t>B | 337呎 (1房)
 $909万
 $26,961/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -33958,7 +33958,7 @@
           <t>C | 440呎 (2房)
 $1190万
 $27,048/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -33981,7 +33981,7 @@
           <t>A | 577呎 (2房)
 $1846万
 $31,991/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -33989,7 +33989,7 @@
           <t>B | 337呎 (1房)
 $907万
 $26,908/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -33997,7 +33997,7 @@
           <t>C | 440呎 (2房)
 $1244万
 $28,264/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -34005,7 +34005,7 @@
           <t>D | 340呎 (1房)
 $954万
 $28,047/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34020,7 @@
           <t>A | 577呎 (2房)
 $1758万
 $30,463/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>B | 337呎 (1房)
 $952万
 $28,255/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>C | 440呎 (2房)
 $1247万
 $28,345/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -34059,7 +34059,7 @@
           <t>A | 577呎 (2房)
 $1752万
 $30,371/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -34067,7 +34067,7 @@
           <t>B | 337呎 (1房)
 $908万
 $26,932/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -34075,7 +34075,7 @@
           <t>C | 440呎 (2房)
 $1189万
 $27,018/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -34098,7 +34098,7 @@
           <t>A | 577呎 (2房)
 $1742万
 $30,191/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -34106,7 +34106,7 @@
           <t>B | 337呎 (1房)
 $904万
 $26,822/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -34114,7 +34114,7 @@
           <t>C | 440呎 (2房)
 $1226万
 $27,859/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -34137,7 +34137,7 @@
           <t>A | 577呎 (2房)
 $1767万
 $30,631/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -34145,7 +34145,7 @@
           <t>B | 337呎 (1房)
 $918万
 $27,243/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -34153,7 +34153,7 @@
           <t>C | 440呎 (2房)
 $1182万
 $26,855/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -34176,7 +34176,7 @@
           <t>A | 577呎 (2房)
 $1732万
 $30,010/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -34184,7 +34184,7 @@
           <t>B | 337呎 (1房)
 $904万
 $26,822/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -34192,7 +34192,7 @@
           <t>C | 440呎 (2房)
 $1218万
 $27,693/呎
-(26年-03月-27日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -34215,7 +34215,7 @@
           <t>A | 577呎 (2房)
 $1721万
 $29,830/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -34223,7 +34223,7 @@
           <t>B | 337呎 (1房)
 $897万
 $26,611/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -34231,7 +34231,7 @@
           <t>C | 440呎 (2房)
 $1230万
 $27,952/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -34262,7 +34262,7 @@
           <t>B | 337呎 (1房)
 $895万
 $26,555/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -34270,7 +34270,7 @@
           <t>C | 440呎 (2房)
 $1172万
 $26,643/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -34301,7 +34301,7 @@
           <t>B | 337呎 (1房)
 $893万
 $26,501/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -34309,7 +34309,7 @@
           <t>C | 440呎 (2房)
 $1225万
 $27,841/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -34332,7 +34332,7 @@
           <t>A | 577呎 (2房)
 $1706万
 $29,563/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -34340,7 +34340,7 @@
           <t>B | 337呎 (1房)
 $933万
 $27,694/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -34348,7 +34348,7 @@
           <t>C | 440呎 (2房)
 $1168万
 $26,536/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -34356,7 +34356,7 @@
           <t>D | 340呎 (1房)
 $901万
 $26,494/呎
-(26年-07月-04日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -34387,7 +34387,7 @@
           <t>C | 401呎 (2房)
 $1250万
 $31,172/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -34571,7 +34571,7 @@
           <t>E | 399呎 (2房)
 $1145万
 $28,702/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -34610,7 +34610,7 @@
           <t>D | 342呎 (1房)
 $989万
 $28,906/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -34618,7 +34618,7 @@
           <t>E | 399呎 (2房)
 $1183万
 $29,647/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -34665,7 +34665,7 @@
           <t>E | 399呎 (2房)
 $1140万
 $28,576/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -34712,7 +34712,7 @@
           <t>E | 399呎 (2房)
 $1138万
 $28,516/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -34751,7 +34751,7 @@
           <t>D | 342呎 (1房)
 $965万
 $28,225/呎
-(26年-07月-04日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -34759,7 +34759,7 @@
           <t>E | 399呎 (2房)
 $1135万
 $28,456/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34806,7 @@
           <t>E | 399呎 (2房)
 $1170万
 $29,336/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34837,7 @@
           <t>C | 563呎 (2房)
 $1833万
 $32,556/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -34853,7 +34853,7 @@
           <t>E | 399呎 (2房)
 $1125万
 $28,193/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
           <t>C | 563呎 (2房)
 $1796万
 $31,892/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -34892,7 +34892,7 @@
           <t>D | 342呎 (1房)
 $960万
 $28,070/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -34900,7 +34900,7 @@
           <t>E | 399呎 (2房)
 $1123万
 $28,135/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -34947,7 +34947,7 @@
           <t>E | 399呎 (2房)
 $1120万
 $28,075/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -34978,7 +34978,7 @@
           <t>C | 563呎 (2房)
 $1811万
 $32,165/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -34994,7 +34994,7 @@
           <t>E | 399呎 (2房)
 $1157万
 $29,003/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35041,7 +35041,7 @@
           <t>E | 399呎 (2房)
 $1116万
 $27,957/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35072,7 @@
           <t>C | 563呎 (2房)
 $1789万
 $31,778/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -35088,7 +35088,7 @@
           <t>E | 399呎 (2房)
 $1152万
 $28,882/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35119,7 +35119,7 @@
           <t>C | 563呎 (2房)
 $1768万
 $31,394/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -35135,7 +35135,7 @@
           <t>E | 399呎 (2房)
 $1111万
 $27,840/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
           <t>C | 563呎 (2房)
 $1845万
 $32,767/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -35182,7 +35182,7 @@
           <t>E | 399呎 (2房)
 $1161万
 $29,088/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35213,7 +35213,7 @@
           <t>C | 563呎 (2房)
 $1767万
 $31,389/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -35229,7 +35229,7 @@
           <t>E | 399呎 (2房)
 $1156万
 $28,972/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35276,7 +35276,7 @@
           <t>E | 399呎 (2房)
 $1154万
 $28,917/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
           <t>E | 399呎 (2房)
 $1100万
 $27,561/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35354,7 +35354,7 @@
           <t>C | 563呎 (2房)
 $1736万
 $30,829/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -35370,7 +35370,7 @@
           <t>E | 399呎 (2房)
 $1098万
 $27,506/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35401,7 +35401,7 @@
           <t>C | 563呎 (2房)
 $1731万
 $30,739/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -35417,7 +35417,7 @@
           <t>E | 399呎 (2房)
 $1093万
 $27,396/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35448,7 +35448,7 @@
           <t>C | 563呎 (2房)
 $1725万
 $30,647/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -35464,7 +35464,7 @@
           <t>E | 399呎 (2房)
 $1091万
 $27,341/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35495,7 +35495,7 @@
           <t>C | 563呎 (2房)
 $1736万
 $30,829/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -35511,7 +35511,7 @@
           <t>E | 399呎 (2房)
 $1089万
 $27,286/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35542,7 +35542,7 @@
           <t>C | 563呎 (2房)
 $1731万
 $30,739/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -35558,7 +35558,7 @@
           <t>E | 399呎 (2房)
 $1087万
 $27,233/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35589,7 +35589,7 @@
           <t>C | 563呎 (2房)
 $1790万
 $31,801/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -35605,7 +35605,7 @@
           <t>E | 399呎 (2房)
 $1084万
 $27,178/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35636,7 +35636,7 @@
           <t>C | 563呎 (2房)
 $1700万
 $30,190/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -35652,7 +35652,7 @@
           <t>E | 399呎 (2房)
 $1080万
 $27,070/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35683,7 +35683,7 @@
           <t>C | 563呎 (2房)
 $1695万
 $30,099/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -35699,7 +35699,7 @@
           <t>E | 399呎 (2房)
 $1129万
 $28,288/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35730,7 +35730,7 @@
           <t>C | 563呎 (2房)
 $1705万
 $30,282/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -35746,7 +35746,7 @@
           <t>E | 399呎 (2房)
 $1076万
 $26,962/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
           <t>C | 563呎 (2房)
 $1680万
 $29,831/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -35793,7 +35793,7 @@
           <t>E | 399呎 (2房)
 $1074万
 $26,907/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35824,7 +35824,7 @@
           <t>C | 563呎 (2房)
 $1674万
 $29,742/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -35840,7 +35840,7 @@
           <t>E | 399呎 (2房)
 $1078万
 $27,013/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35871,7 +35871,7 @@
           <t>C | 563呎 (2房)
 $1669万
 $29,652/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -35887,7 +35887,7 @@
           <t>E | 399呎 (2房)
 $1107万
 $27,747/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -35918,7 +35918,7 @@
           <t>C | 563呎 (2房)
 $1679万
 $29,829/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -35934,7 +35934,7 @@
           <t>E | 399呎 (2房)
 $1067万
 $26,747/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -35973,7 +35973,7 @@
           <t>D | 304呎 (1房)
 $1021万
 $33,599/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -31523,7 +31523,7 @@
           <t>F | 337呎 (1房)
 $955万
 $28,350/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
           <t>F | 337呎 (1房)
 $942万
 $27,964/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -31633,7 +31633,7 @@
           <t>F | 337呎 (1房)
 $940万
 $27,902/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31688,7 @@
           <t>F | 337呎 (1房)
 $936万
 $27,786/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -31743,7 +31743,7 @@
           <t>F | 337呎 (1房)
 $934万
 $27,727/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -32293,7 +32293,7 @@
           <t>F | 337呎 (1房)
 $957万
 $28,386/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -32403,7 +32403,7 @@
           <t>F | 337呎 (1房)
 $910万
 $27,000/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -32458,7 +32458,7 @@
           <t>F | 337呎 (1房)
 $919万
 $27,261/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32513,7 @@
           <t>F | 337呎 (1房)
 $917万
 $27,208/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
           <t>F | 337呎 (1房)
 $913万
 $27,098/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -32678,7 +32678,7 @@
           <t>F | 337呎 (1房)
 $910万
 $26,991/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -32733,7 +32733,7 @@
           <t>F | 337呎 (1房)
 $897万
 $26,623/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -32788,7 +32788,7 @@
           <t>F | 337呎 (1房)
 $894万
 $26,516/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -32843,7 +32843,7 @@
           <t>F | 337呎 (1房)
 $892万
 $26,466/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
           <t>F | 337呎 (1房)
 $890万
 $26,412/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -32953,7 +32953,7 @@
           <t>F | 337呎 (1房)
 $888万
 $26,359/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -33008,7 +33008,7 @@
           <t>F | 337呎 (1房)
 $918万
 $27,234/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
           <t>B | 337呎 (1房)
 $949万
 $28,163/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -33217,7 +33217,7 @@
           <t>C | 440呎 (2房)
 $1243万
 $28,252/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -33248,7 +33248,7 @@
           <t>B | 337呎 (1房)
 $992万
 $29,421/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -33256,7 +33256,7 @@
           <t>C | 440呎 (2房)
 $1240万
 $28,191/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -33264,7 +33264,7 @@
           <t>D | 340呎 (1房)
 $956万
 $28,115/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -33287,7 +33287,7 @@
           <t>B | 337呎 (1房)
 $989万
 $29,359/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -33295,7 +33295,7 @@
           <t>C | 440呎 (2房)
 $1296万
 $29,452/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -33303,7 +33303,7 @@
           <t>D | 340呎 (1房)
 $999万
 $29,371/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -33318,7 +33318,7 @@
           <t>A | 577呎 (2房)
 $1935万
 $33,541/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -33326,7 +33326,7 @@
           <t>B | 337呎 (1房)
 $943万
 $27,982/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -33334,7 +33334,7 @@
           <t>C | 440呎 (2房)
 $1235万
 $28,070/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -33342,7 +33342,7 @@
           <t>D | 340呎 (1房)
 $996万
 $29,309/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
           <t>A | 577呎 (2房)
 $1863万
 $32,295/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -33365,7 +33365,7 @@
           <t>B | 337呎 (1房)
 $941万
 $27,920/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -33373,7 +33373,7 @@
           <t>C | 440呎 (2房)
 $1232万
 $28,011/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -33381,7 +33381,7 @@
           <t>D | 340呎 (1房)
 $950万
 $27,935/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -33404,7 +33404,7 @@
           <t>B | 337呎 (1房)
 $954万
 $28,294/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -33412,7 +33412,7 @@
           <t>C | 440呎 (2房)
 $1227万
 $27,895/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -33420,7 +33420,7 @@
           <t>D | 340呎 (1房)
 $946万
 $27,818/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -33435,7 +33435,7 @@
           <t>A | 577呎 (2房)
 $1846万
 $31,991/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -33443,7 +33443,7 @@
           <t>B | 337呎 (1房)
 $935万
 $27,745/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -33451,7 +33451,7 @@
           <t>C | 440呎 (2房)
 $1225万
 $27,834/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -33459,7 +33459,7 @@
           <t>D | 340呎 (1房)
 $941万
 $27,676/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -33474,7 +33474,7 @@
           <t>A | 577呎 (2房)
 $1840万
 $31,891/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -33482,7 +33482,7 @@
           <t>B | 337呎 (1房)
 $933万
 $27,688/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -33490,7 +33490,7 @@
           <t>C | 440呎 (2房)
 $1222万
 $27,777/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -33498,7 +33498,7 @@
           <t>D | 340呎 (1房)
 $939万
 $27,618/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -33513,7 +33513,7 @@
           <t>A | 577呎 (2房)
 $1834万
 $31,790/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -33521,7 +33521,7 @@
           <t>B | 337呎 (1房)
 $975万
 $28,932/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -33529,7 +33529,7 @@
           <t>C | 440呎 (2房)
 $1277万
 $29,023/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -33537,7 +33537,7 @@
           <t>D | 340呎 (1房)
 $937万
 $27,559/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -33552,7 +33552,7 @@
           <t>A | 577呎 (2房)
 $1829万
 $31,692/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -33560,7 +33560,7 @@
           <t>B | 337呎 (1房)
 $929万
 $27,573/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -33568,7 +33568,7 @@
           <t>C | 440呎 (2房)
 $1260万
 $28,636/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -33576,7 +33576,7 @@
           <t>D | 340呎 (1房)
 $979万
 $28,794/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
           <t>A | 577呎 (2房)
 $1844万
 $31,964/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -33599,7 +33599,7 @@
           <t>B | 337呎 (1房)
 $927万
 $27,513/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -33607,7 +33607,7 @@
           <t>C | 440呎 (2房)
 $1272万
 $28,902/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -33638,7 +33638,7 @@
           <t>B | 337呎 (1房)
 $925万
 $27,457/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -33646,7 +33646,7 @@
           <t>C | 440呎 (2房)
 $1212万
 $27,545/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>B | 337呎 (1房)
 $923万
 $27,398/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -33685,7 +33685,7 @@
           <t>C | 440呎 (2房)
 $1209万
 $27,486/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>A | 577呎 (2房)
 $1869万
 $32,399/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>B | 337呎 (1房)
 $921万
 $27,341/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -33724,7 +33724,7 @@
           <t>C | 440呎 (2房)
 $1250万
 $28,398/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -33747,7 +33747,7 @@
           <t>A | 577呎 (2房)
 $1795万
 $31,107/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -33755,7 +33755,7 @@
           <t>B | 337呎 (1房)
 $934万
 $27,715/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -33763,7 +33763,7 @@
           <t>C | 440呎 (2房)
 $1202万
 $27,320/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -33786,7 +33786,7 @@
           <t>A | 577呎 (2房)
 $1874万
 $32,475/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -33794,7 +33794,7 @@
           <t>B | 337呎 (1房)
 $948万
 $28,136/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -33802,7 +33802,7 @@
           <t>C | 440呎 (2房)
 $1200万
 $27,266/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -33810,7 +33810,7 @@
           <t>D | 340呎 (1房)
 $965万
 $28,385/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -33825,7 +33825,7 @@
           <t>A | 577呎 (2房)
 $1784万
 $30,922/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -33833,7 +33833,7 @@
           <t>B | 337呎 (1房)
 $957万
 $28,401/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -33841,7 +33841,7 @@
           <t>C | 440呎 (2房)
 $1197万
 $27,211/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -33864,7 +33864,7 @@
           <t>A | 577呎 (2房)
 $1779万
 $30,830/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -33872,7 +33872,7 @@
           <t>B | 337呎 (1房)
 $955万
 $28,344/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -33880,7 +33880,7 @@
           <t>C | 440呎 (2房)
 $1195万
 $27,157/呎
-(26年-03月)</t>
+(26年-03月-21日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -33903,7 +33903,7 @@
           <t>A | 577呎 (2房)
 $1774万
 $30,738/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -33911,7 +33911,7 @@
           <t>B | 337呎 (1房)
 $953万
 $28,288/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -33919,7 +33919,7 @@
           <t>C | 440呎 (2房)
 $1192万
 $27,102/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -33942,7 +33942,7 @@
           <t>A | 577呎 (2房)
 $1831万
 $31,728/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -33950,7 +33950,7 @@
           <t>B | 337呎 (1房)
 $909万
 $26,961/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -33958,7 +33958,7 @@
           <t>C | 440呎 (2房)
 $1190万
 $27,048/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -33981,7 +33981,7 @@
           <t>A | 577呎 (2房)
 $1846万
 $31,991/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -33989,7 +33989,7 @@
           <t>B | 337呎 (1房)
 $907万
 $26,908/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -33997,7 +33997,7 @@
           <t>C | 440呎 (2房)
 $1244万
 $28,264/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -34005,7 +34005,7 @@
           <t>D | 340呎 (1房)
 $954万
 $28,047/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34020,7 @@
           <t>A | 577呎 (2房)
 $1758万
 $30,463/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>B | 337呎 (1房)
 $952万
 $28,255/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>C | 440呎 (2房)
 $1247万
 $28,345/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -34059,7 +34059,7 @@
           <t>A | 577呎 (2房)
 $1752万
 $30,371/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -34067,7 +34067,7 @@
           <t>B | 337呎 (1房)
 $908万
 $26,932/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -34075,7 +34075,7 @@
           <t>C | 440呎 (2房)
 $1189万
 $27,018/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -34098,7 +34098,7 @@
           <t>A | 577呎 (2房)
 $1742万
 $30,191/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -34106,7 +34106,7 @@
           <t>B | 337呎 (1房)
 $904万
 $26,822/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -34114,7 +34114,7 @@
           <t>C | 440呎 (2房)
 $1226万
 $27,859/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -34137,7 +34137,7 @@
           <t>A | 577呎 (2房)
 $1767万
 $30,631/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -34145,7 +34145,7 @@
           <t>B | 337呎 (1房)
 $918万
 $27,243/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -34153,7 +34153,7 @@
           <t>C | 440呎 (2房)
 $1182万
 $26,855/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -34176,7 +34176,7 @@
           <t>A | 577呎 (2房)
 $1732万
 $30,010/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -34184,7 +34184,7 @@
           <t>B | 337呎 (1房)
 $904万
 $26,822/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -34192,7 +34192,7 @@
           <t>C | 440呎 (2房)
 $1218万
 $27,693/呎
-(26年-03月)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -34215,7 +34215,7 @@
           <t>A | 577呎 (2房)
 $1721万
 $29,830/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -34223,7 +34223,7 @@
           <t>B | 337呎 (1房)
 $897万
 $26,611/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -34231,7 +34231,7 @@
           <t>C | 440呎 (2房)
 $1230万
 $27,952/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -34262,7 +34262,7 @@
           <t>B | 337呎 (1房)
 $895万
 $26,555/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -34270,7 +34270,7 @@
           <t>C | 440呎 (2房)
 $1172万
 $26,643/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -34301,7 +34301,7 @@
           <t>B | 337呎 (1房)
 $893万
 $26,501/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -34309,7 +34309,7 @@
           <t>C | 440呎 (2房)
 $1225万
 $27,841/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -34332,7 +34332,7 @@
           <t>A | 577呎 (2房)
 $1706万
 $29,563/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -34340,7 +34340,7 @@
           <t>B | 337呎 (1房)
 $933万
 $27,694/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -34348,7 +34348,7 @@
           <t>C | 440呎 (2房)
 $1168万
 $26,536/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -34356,7 +34356,7 @@
           <t>D | 340呎 (1房)
 $901万
 $26,494/呎
-(26年-07月)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -34387,7 +34387,7 @@
           <t>C | 401呎 (2房)
 $1250万
 $31,172/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -34571,7 +34571,7 @@
           <t>E | 399呎 (2房)
 $1145万
 $28,702/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -34610,7 +34610,7 @@
           <t>D | 342呎 (1房)
 $989万
 $28,906/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -34618,7 +34618,7 @@
           <t>E | 399呎 (2房)
 $1183万
 $29,647/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -34665,7 +34665,7 @@
           <t>E | 399呎 (2房)
 $1140万
 $28,576/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -34712,7 +34712,7 @@
           <t>E | 399呎 (2房)
 $1138万
 $28,516/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -34751,7 +34751,7 @@
           <t>D | 342呎 (1房)
 $965万
 $28,225/呎
-(26年-07月)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -34759,7 +34759,7 @@
           <t>E | 399呎 (2房)
 $1135万
 $28,456/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -34806,7 +34806,7 @@
           <t>E | 399呎 (2房)
 $1170万
 $29,336/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34837,7 @@
           <t>C | 563呎 (2房)
 $1833万
 $32,556/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -34853,7 +34853,7 @@
           <t>E | 399呎 (2房)
 $1125万
 $28,193/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
           <t>C | 563呎 (2房)
 $1796万
 $31,892/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -34892,7 +34892,7 @@
           <t>D | 342呎 (1房)
 $960万
 $28,070/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -34900,7 +34900,7 @@
           <t>E | 399呎 (2房)
 $1123万
 $28,135/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -34947,7 +34947,7 @@
           <t>E | 399呎 (2房)
 $1120万
 $28,075/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -34978,7 +34978,7 @@
           <t>C | 563呎 (2房)
 $1811万
 $32,165/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -34994,7 +34994,7 @@
           <t>E | 399呎 (2房)
 $1157万
 $29,003/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -35041,7 +35041,7 @@
           <t>E | 399呎 (2房)
 $1116万
 $27,957/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35072,7 @@
           <t>C | 563呎 (2房)
 $1789万
 $31,778/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -35088,7 +35088,7 @@
           <t>E | 399呎 (2房)
 $1152万
 $28,882/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -35119,7 +35119,7 @@
           <t>C | 563呎 (2房)
 $1768万
 $31,394/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -35135,7 +35135,7 @@
           <t>E | 399呎 (2房)
 $1111万
 $27,840/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
           <t>C | 563呎 (2房)
 $1845万
 $32,767/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -35182,7 +35182,7 @@
           <t>E | 399呎 (2房)
 $1161万
 $29,088/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -35213,7 +35213,7 @@
           <t>C | 563呎 (2房)
 $1767万
 $31,389/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -35229,7 +35229,7 @@
           <t>E | 399呎 (2房)
 $1156万
 $28,972/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -35276,7 +35276,7 @@
           <t>E | 399呎 (2房)
 $1154万
 $28,917/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
           <t>E | 399呎 (2房)
 $1100万
 $27,561/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -35354,7 +35354,7 @@
           <t>C | 563呎 (2房)
 $1736万
 $30,829/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -35370,7 +35370,7 @@
           <t>E | 399呎 (2房)
 $1098万
 $27,506/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -35401,7 +35401,7 @@
           <t>C | 563呎 (2房)
 $1731万
 $30,739/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -35417,7 +35417,7 @@
           <t>E | 399呎 (2房)
 $1093万
 $27,396/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -35448,7 +35448,7 @@
           <t>C | 563呎 (2房)
 $1725万
 $30,647/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -35464,7 +35464,7 @@
           <t>E | 399呎 (2房)
 $1091万
 $27,341/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -35495,7 +35495,7 @@
           <t>C | 563呎 (2房)
 $1736万
 $30,829/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -35511,7 +35511,7 @@
           <t>E | 399呎 (2房)
 $1089万
 $27,286/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -35542,7 +35542,7 @@
           <t>C | 563呎 (2房)
 $1731万
 $30,739/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -35558,7 +35558,7 @@
           <t>E | 399呎 (2房)
 $1087万
 $27,233/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -35589,7 +35589,7 @@
           <t>C | 563呎 (2房)
 $1790万
 $31,801/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -35605,7 +35605,7 @@
           <t>E | 399呎 (2房)
 $1084万
 $27,178/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -35636,7 +35636,7 @@
           <t>C | 563呎 (2房)
 $1700万
 $30,190/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -35652,7 +35652,7 @@
           <t>E | 399呎 (2房)
 $1080万
 $27,070/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -35683,7 +35683,7 @@
           <t>C | 563呎 (2房)
 $1695万
 $30,099/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -35699,7 +35699,7 @@
           <t>E | 399呎 (2房)
 $1129万
 $28,288/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -35730,7 +35730,7 @@
           <t>C | 563呎 (2房)
 $1705万
 $30,282/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -35746,7 +35746,7 @@
           <t>E | 399呎 (2房)
 $1076万
 $26,962/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
           <t>C | 563呎 (2房)
 $1680万
 $29,831/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -35793,7 +35793,7 @@
           <t>E | 399呎 (2房)
 $1074万
 $26,907/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -35824,7 +35824,7 @@
           <t>C | 563呎 (2房)
 $1674万
 $29,742/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -35840,7 +35840,7 @@
           <t>E | 399呎 (2房)
 $1078万
 $27,013/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -35871,7 +35871,7 @@
           <t>C | 563呎 (2房)
 $1669万
 $29,652/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -35887,7 +35887,7 @@
           <t>E | 399呎 (2房)
 $1107万
 $27,747/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -35918,7 +35918,7 @@
           <t>C | 563呎 (2房)
 $1679万
 $29,829/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -35934,7 +35934,7 @@
           <t>E | 399呎 (2房)
 $1067万
 $26,747/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -35973,7 +35973,7 @@
           <t>D | 304呎 (1房)
 $1021万
 $33,599/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
@@ -12989,38 +12989,30 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>9120000</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>30400</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L181" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K181" s="5" t="n">
+        <v>9120000</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>30400</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -13029,7 +13021,7 @@
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13417,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
@@ -13611,7 +13603,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
@@ -13859,7 +13851,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
@@ -14107,7 +14099,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
@@ -14851,7 +14843,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
@@ -15905,7 +15897,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
@@ -16153,7 +16145,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
@@ -16339,7 +16331,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
@@ -16401,7 +16393,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
@@ -16587,7 +16579,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
@@ -16649,7 +16641,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
@@ -16897,7 +16889,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
@@ -17393,7 +17385,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
@@ -17641,7 +17633,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K255" s="5" t="n">
@@ -17889,7 +17881,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
@@ -18137,7 +18129,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
@@ -20307,7 +20299,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K298" s="5" t="n">
@@ -20555,7 +20547,7 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K302" s="5" t="n">
@@ -20606,7 +20598,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -21913,7 +21905,7 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
@@ -22239,7 +22231,7 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K328" s="5" t="n">
@@ -22492,7 +22484,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -24184,14 +24176,14 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
-        <v>18109000</v>
+        <v>18003000</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>32165</v>
+        <v>31977</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
@@ -24199,10 +24191,10 @@
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>18109000</v>
+        <v>18003000</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>32165</v>
+        <v>31977</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
@@ -31315,7 +31307,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31325,7 +31317,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31523,7 +31515,7 @@
           <t>F | 337呎 (1房)
 $955万
 $28,350/呎
-(26年-06月-29日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
     </row>
@@ -33058,12 +33050,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>F | 300呎 (1房)
-招标单位
--
-(在售)</t>
+$912万
+$30,400/呎
+(26年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34348,7 @@
           <t>D | 340呎 (1房)
 $901万
 $26,494/呎
-(26年-07月-04日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
     </row>
@@ -34751,7 +34743,7 @@
           <t>D | 342呎 (1房)
 $965万
 $28,225/呎
-(26年-07月-04日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -34976,9 +34968,9 @@
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 563呎 (2房)
-$1811万
-$32,165/呎
-(26年-06月-25日)</t>
+$1800万
+$31,977/呎
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
